--- a/backend/tests/fixtures/排課母版_v6.xlsx
+++ b/backend/tests/fixtures/排課母版_v6.xlsx
@@ -2,14 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="1" r:id="Rb95163a218aa4206"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="學校基本資料" sheetId="2" r:id="R4192f7d822c9449b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="班級" sheetId="3" r:id="R2d9f9e86d0404a3b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教師與配課" sheetId="4" r:id="R8ab217c5a6f143ee"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="場地" sheetId="5" r:id="Rde7fb6b233bb4d89"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科目節數" sheetId="6" r:id="R599e082a45e341b7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年段時段" sheetId="7" r:id="R8e1cec63d4eb46d4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本土語分組" sheetId="8" r:id="Rdc0b547117bb4243"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="說明" sheetId="1" r:id="Rc49d518d1cb24801"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="學校基本資料" sheetId="2" r:id="Rd635427bda5845df"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="班級" sheetId="3" r:id="Rec46a8abbaeb4db0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="教師與配課" sheetId="4" r:id="R07002f2c9339499d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="場地" sheetId="5" r:id="R8de9ea86916d4d4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="科目節數" sheetId="6" r:id="Rcd46316032544273"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="年段時段" sheetId="7" r:id="Rc36b9f426be94929"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="本土語分組" sheetId="8" r:id="R1cb47cf7f9074a79"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="資源班課表" sheetId="9" r:id="R7f40a0c1921b44b7"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -20,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="11">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -80,8 +81,18 @@
       <x:color rgb="FF487B99"/>
       <x:name val="Microsoft JhengHei"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF2F6F9F"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF2F6F9F"/>
+      <x:name val="Microsoft JhengHei"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="10">
+  <x:fills count="13">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -126,6 +137,21 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFFFFFFF"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC2557F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC2557F"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFC2557F"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -205,7 +231,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="53">
+  <x:cellXfs count="66">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -331,6 +357,41 @@
       <x:alignment vertical="center"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="10" fillId="9" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="11" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
@@ -569,7 +630,7 @@
     </x:row>
     <x:row r="3" ht="25" customHeight="1">
       <x:c r="A3" s="8" t="str">
-        <x:v>填寫順序：①學校基本資料 ②班級 ③教師與配課 ④場地 ⑤科目節數。年段時段與本土語分組可依實際需求調整。</x:v>
+        <x:v>填寫順序：①學校基本資料 ②班級 ③教師與配課 ④場地 ⑤科目節數 ⑥資源班課表。年段時段與本土語分組可依實際需求調整。</x:v>
       </x:c>
       <x:c r="B3" s="9" t="str">
         <x:v>填寫順序：①學校基本資料 ②班級 ③教師與配課 ④場地 ⑤科目節數。年段時段與本土語分組可依實際需求調整。</x:v>
@@ -933,7 +994,7 @@
     </x:row>
     <x:row r="17" ht="25" customHeight="1">
       <x:c r="A17" s="8" t="str">
-        <x:v>填寫完成後先在 Excel 儲存，再回到智慧排課系統按「從 Excel 匯入」。上傳後請到配課檢核查看缺配與教師節數。</x:v>
+        <x:v>若已有資源班課表，請在「資源班課表」逐節填入來源班級、國語文／數學、教師與固定時段；匯入後會自動勾選來源班級並綁定原班同科節次。</x:v>
       </x:c>
       <x:c r="B17" s="9" t="str">
         <x:v>填寫完成後先在 Excel 儲存，再回到智慧排課系統按「從 Excel 匯入」。上傳後請到配課檢核查看缺配與教師節數。</x:v>
@@ -1740,13 +1801,21 @@
       <x:c r="K10" s="35"/>
     </x:row>
     <x:row r="11" ht="25" customHeight="1">
-      <x:c r="A11" s="35"/>
-      <x:c r="B11" s="35"/>
+      <x:c r="A11" s="35" t="str">
+        <x:v>資源教師</x:v>
+      </x:c>
+      <x:c r="B11" s="35" t="str">
+        <x:v>資源班教師</x:v>
+      </x:c>
       <x:c r="C11" s="35"/>
-      <x:c r="D11" s="35"/>
+      <x:c r="D11" s="35" t="n">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="E11" s="35"/>
       <x:c r="F11" s="35"/>
-      <x:c r="G11" s="35"/>
+      <x:c r="G11" s="35" t="str">
+        <x:v>資源班課表範例</x:v>
+      </x:c>
       <x:c r="H11" s="25"/>
       <x:c r="I11" s="35"/>
       <x:c r="J11" s="35"/>
@@ -6737,4 +6806,349 @@
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="23" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="12" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="12" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="34" customHeight="1">
+      <x:c r="A1" s="64" t="str">
+        <x:v>分組名稱</x:v>
+      </x:c>
+      <x:c r="B1" s="64" t="str">
+        <x:v>來源班級</x:v>
+      </x:c>
+      <x:c r="C1" s="64" t="str">
+        <x:v>資源班授課科目</x:v>
+      </x:c>
+      <x:c r="D1" s="64" t="str">
+        <x:v>資源班教師</x:v>
+      </x:c>
+      <x:c r="E1" s="64" t="str">
+        <x:v>星期 ▾</x:v>
+      </x:c>
+      <x:c r="F1" s="64" t="str">
+        <x:v>節次 ▾</x:v>
+      </x:c>
+      <x:c r="G1" s="64" t="str">
+        <x:v>原班綁定科目</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="24" customHeight="1">
+      <x:c r="A2" s="65" t="str">
+        <x:v>1年級國語組</x:v>
+      </x:c>
+      <x:c r="B2" s="65" t="str">
+        <x:v>1甲、1乙</x:v>
+      </x:c>
+      <x:c r="C2" s="65" t="str">
+        <x:v>國語文</x:v>
+      </x:c>
+      <x:c r="D2" s="65" t="str">
+        <x:v>資源教師</x:v>
+      </x:c>
+      <x:c r="E2" s="65" t="str">
+        <x:v>一</x:v>
+      </x:c>
+      <x:c r="F2" s="65" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="G2" s="65" t="str">
+        <x:v>國語文</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="24" customHeight="1">
+      <x:c r="A3" s="65" t="str">
+        <x:v>1年級數學組</x:v>
+      </x:c>
+      <x:c r="B3" s="65" t="str">
+        <x:v>1甲、1乙</x:v>
+      </x:c>
+      <x:c r="C3" s="65" t="str">
+        <x:v>數學</x:v>
+      </x:c>
+      <x:c r="D3" s="65" t="str">
+        <x:v>資源教師</x:v>
+      </x:c>
+      <x:c r="E3" s="65" t="str">
+        <x:v>三</x:v>
+      </x:c>
+      <x:c r="F3" s="65" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="G3" s="65" t="str">
+        <x:v>數學</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="24" customHeight="1">
+      <x:c r="A4" s="65"/>
+      <x:c r="B4" s="65"/>
+      <x:c r="C4" s="65"/>
+      <x:c r="D4" s="65"/>
+      <x:c r="E4" s="65"/>
+      <x:c r="F4" s="65"/>
+      <x:c r="G4" s="65"/>
+    </x:row>
+    <x:row r="5" ht="24" customHeight="1">
+      <x:c r="A5" s="65"/>
+      <x:c r="B5" s="65"/>
+      <x:c r="C5" s="65"/>
+      <x:c r="D5" s="65"/>
+      <x:c r="E5" s="65"/>
+      <x:c r="F5" s="65"/>
+      <x:c r="G5" s="65"/>
+    </x:row>
+    <x:row r="6" ht="24" customHeight="1">
+      <x:c r="A6" s="65"/>
+      <x:c r="B6" s="65"/>
+      <x:c r="C6" s="65"/>
+      <x:c r="D6" s="65"/>
+      <x:c r="E6" s="65"/>
+      <x:c r="F6" s="65"/>
+      <x:c r="G6" s="65"/>
+    </x:row>
+    <x:row r="7" ht="24" customHeight="1">
+      <x:c r="A7" s="65"/>
+      <x:c r="B7" s="65"/>
+      <x:c r="C7" s="65"/>
+      <x:c r="D7" s="65"/>
+      <x:c r="E7" s="65"/>
+      <x:c r="F7" s="65"/>
+      <x:c r="G7" s="65"/>
+    </x:row>
+    <x:row r="8" ht="24" customHeight="1">
+      <x:c r="A8" s="65"/>
+      <x:c r="B8" s="65"/>
+      <x:c r="C8" s="65"/>
+      <x:c r="D8" s="65"/>
+      <x:c r="E8" s="65"/>
+      <x:c r="F8" s="65"/>
+      <x:c r="G8" s="65"/>
+    </x:row>
+    <x:row r="9" ht="24" customHeight="1">
+      <x:c r="A9" s="65"/>
+      <x:c r="B9" s="65"/>
+      <x:c r="C9" s="65"/>
+      <x:c r="D9" s="65"/>
+      <x:c r="E9" s="65"/>
+      <x:c r="F9" s="65"/>
+      <x:c r="G9" s="65"/>
+    </x:row>
+    <x:row r="10" ht="24" customHeight="1">
+      <x:c r="A10" s="65"/>
+      <x:c r="B10" s="65"/>
+      <x:c r="C10" s="65"/>
+      <x:c r="D10" s="65"/>
+      <x:c r="E10" s="65"/>
+      <x:c r="F10" s="65"/>
+      <x:c r="G10" s="65"/>
+    </x:row>
+    <x:row r="11" ht="24" customHeight="1">
+      <x:c r="A11" s="65"/>
+      <x:c r="B11" s="65"/>
+      <x:c r="C11" s="65"/>
+      <x:c r="D11" s="65"/>
+      <x:c r="E11" s="65"/>
+      <x:c r="F11" s="65"/>
+      <x:c r="G11" s="65"/>
+    </x:row>
+    <x:row r="12" ht="24" customHeight="1">
+      <x:c r="A12" s="65"/>
+      <x:c r="B12" s="65"/>
+      <x:c r="C12" s="65"/>
+      <x:c r="D12" s="65"/>
+      <x:c r="E12" s="65"/>
+      <x:c r="F12" s="65"/>
+      <x:c r="G12" s="65"/>
+    </x:row>
+    <x:row r="13" ht="24" customHeight="1">
+      <x:c r="A13" s="65"/>
+      <x:c r="B13" s="65"/>
+      <x:c r="C13" s="65"/>
+      <x:c r="D13" s="65"/>
+      <x:c r="E13" s="65"/>
+      <x:c r="F13" s="65"/>
+      <x:c r="G13" s="65"/>
+    </x:row>
+    <x:row r="14" ht="24" customHeight="1">
+      <x:c r="A14" s="65"/>
+      <x:c r="B14" s="65"/>
+      <x:c r="C14" s="65"/>
+      <x:c r="D14" s="65"/>
+      <x:c r="E14" s="65"/>
+      <x:c r="F14" s="65"/>
+      <x:c r="G14" s="65"/>
+    </x:row>
+    <x:row r="15" ht="24" customHeight="1">
+      <x:c r="A15" s="65"/>
+      <x:c r="B15" s="65"/>
+      <x:c r="C15" s="65"/>
+      <x:c r="D15" s="65"/>
+      <x:c r="E15" s="65"/>
+      <x:c r="F15" s="65"/>
+      <x:c r="G15" s="65"/>
+    </x:row>
+    <x:row r="16" ht="24" customHeight="1">
+      <x:c r="A16" s="65"/>
+      <x:c r="B16" s="65"/>
+      <x:c r="C16" s="65"/>
+      <x:c r="D16" s="65"/>
+      <x:c r="E16" s="65"/>
+      <x:c r="F16" s="65"/>
+      <x:c r="G16" s="65"/>
+    </x:row>
+    <x:row r="17" ht="24" customHeight="1">
+      <x:c r="A17" s="65"/>
+      <x:c r="B17" s="65"/>
+      <x:c r="C17" s="65"/>
+      <x:c r="D17" s="65"/>
+      <x:c r="E17" s="65"/>
+      <x:c r="F17" s="65"/>
+      <x:c r="G17" s="65"/>
+    </x:row>
+    <x:row r="18" ht="24" customHeight="1">
+      <x:c r="A18" s="65"/>
+      <x:c r="B18" s="65"/>
+      <x:c r="C18" s="65"/>
+      <x:c r="D18" s="65"/>
+      <x:c r="E18" s="65"/>
+      <x:c r="F18" s="65"/>
+      <x:c r="G18" s="65"/>
+    </x:row>
+    <x:row r="19" ht="24" customHeight="1">
+      <x:c r="A19" s="65"/>
+      <x:c r="B19" s="65"/>
+      <x:c r="C19" s="65"/>
+      <x:c r="D19" s="65"/>
+      <x:c r="E19" s="65"/>
+      <x:c r="F19" s="65"/>
+      <x:c r="G19" s="65"/>
+    </x:row>
+    <x:row r="20" ht="24" customHeight="1">
+      <x:c r="A20" s="65"/>
+      <x:c r="B20" s="65"/>
+      <x:c r="C20" s="65"/>
+      <x:c r="D20" s="65"/>
+      <x:c r="E20" s="65"/>
+      <x:c r="F20" s="65"/>
+      <x:c r="G20" s="65"/>
+    </x:row>
+    <x:row r="21" ht="24" customHeight="1">
+      <x:c r="A21" s="65"/>
+      <x:c r="B21" s="65"/>
+      <x:c r="C21" s="65"/>
+      <x:c r="D21" s="65"/>
+      <x:c r="E21" s="65"/>
+      <x:c r="F21" s="65"/>
+      <x:c r="G21" s="65"/>
+    </x:row>
+    <x:row r="22" ht="24" customHeight="1">
+      <x:c r="A22" s="65"/>
+      <x:c r="B22" s="65"/>
+      <x:c r="C22" s="65"/>
+      <x:c r="D22" s="65"/>
+      <x:c r="E22" s="65"/>
+      <x:c r="F22" s="65"/>
+      <x:c r="G22" s="65"/>
+    </x:row>
+    <x:row r="23" ht="24" customHeight="1">
+      <x:c r="A23" s="65"/>
+      <x:c r="B23" s="65"/>
+      <x:c r="C23" s="65"/>
+      <x:c r="D23" s="65"/>
+      <x:c r="E23" s="65"/>
+      <x:c r="F23" s="65"/>
+      <x:c r="G23" s="65"/>
+    </x:row>
+    <x:row r="24" ht="24" customHeight="1">
+      <x:c r="A24" s="65"/>
+      <x:c r="B24" s="65"/>
+      <x:c r="C24" s="65"/>
+      <x:c r="D24" s="65"/>
+      <x:c r="E24" s="65"/>
+      <x:c r="F24" s="65"/>
+      <x:c r="G24" s="65"/>
+    </x:row>
+    <x:row r="25" ht="24" customHeight="1">
+      <x:c r="A25" s="65"/>
+      <x:c r="B25" s="65"/>
+      <x:c r="C25" s="65"/>
+      <x:c r="D25" s="65"/>
+      <x:c r="E25" s="65"/>
+      <x:c r="F25" s="65"/>
+      <x:c r="G25" s="65"/>
+    </x:row>
+    <x:row r="26" ht="24" customHeight="1">
+      <x:c r="A26" s="65"/>
+      <x:c r="B26" s="65"/>
+      <x:c r="C26" s="65"/>
+      <x:c r="D26" s="65"/>
+      <x:c r="E26" s="65"/>
+      <x:c r="F26" s="65"/>
+      <x:c r="G26" s="65"/>
+    </x:row>
+    <x:row r="27" ht="24" customHeight="1">
+      <x:c r="A27" s="65"/>
+      <x:c r="B27" s="65"/>
+      <x:c r="C27" s="65"/>
+      <x:c r="D27" s="65"/>
+      <x:c r="E27" s="65"/>
+      <x:c r="F27" s="65"/>
+      <x:c r="G27" s="65"/>
+    </x:row>
+    <x:row r="28" ht="24" customHeight="1">
+      <x:c r="A28" s="65"/>
+      <x:c r="B28" s="65"/>
+      <x:c r="C28" s="65"/>
+      <x:c r="D28" s="65"/>
+      <x:c r="E28" s="65"/>
+      <x:c r="F28" s="65"/>
+      <x:c r="G28" s="65"/>
+    </x:row>
+    <x:row r="29" ht="24" customHeight="1">
+      <x:c r="A29" s="65"/>
+      <x:c r="B29" s="65"/>
+      <x:c r="C29" s="65"/>
+      <x:c r="D29" s="65"/>
+      <x:c r="E29" s="65"/>
+      <x:c r="F29" s="65"/>
+      <x:c r="G29" s="65"/>
+    </x:row>
+    <x:row r="30" ht="24" customHeight="1">
+      <x:c r="A30" s="65"/>
+      <x:c r="B30" s="65"/>
+      <x:c r="C30" s="65"/>
+      <x:c r="D30" s="65"/>
+      <x:c r="E30" s="65"/>
+      <x:c r="F30" s="65"/>
+      <x:c r="G30" s="65"/>
+    </x:row>
+  </x:sheetData>
+  <x:dataValidations count="4">
+    <x:dataValidation type="list" sqref="C2:C100">
+      <x:formula1>"國語文,數學"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="E2:E100">
+      <x:formula1>"一,二,三,四,五"</x:formula1>
+    </x:dataValidation>
+    <x:dataValidation type="whole" operator="between" sqref="F2:F100">
+      <x:formula1>0</x:formula1>
+      <x:formula2>7</x:formula2>
+    </x:dataValidation>
+    <x:dataValidation type="list" sqref="G2:G100">
+      <x:formula1>"國語文,數學"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
 </file>